--- a/data/trans_dic/P25A$medico-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 26,74</t>
+          <t>10,82; 27,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 25,62</t>
+          <t>10,99; 25,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 28,74</t>
+          <t>10,38; 28,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,44</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 22,85</t>
+          <t>4,83; 20,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 21,6</t>
+          <t>7,92; 20,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 18,85</t>
+          <t>7,83; 18,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 22,96</t>
+          <t>10,42; 22,93</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 24,24</t>
+          <t>8,11; 23,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 17,19</t>
+          <t>4,34; 17,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 25,85</t>
+          <t>7,81; 24,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,62</t>
+          <t>0,0; 15,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,05</t>
+          <t>0,0; 17,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 25,58</t>
+          <t>6,66; 25,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 17,84</t>
+          <t>6,43; 18,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,66</t>
+          <t>3,71; 13,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,05; 22,0</t>
+          <t>9,63; 21,63</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 32,63</t>
+          <t>16,43; 32,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,23; 25,66</t>
+          <t>12,35; 26,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 28,86</t>
+          <t>12,87; 28,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,42</t>
+          <t>0,0; 22,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,2</t>
+          <t>2,69; 23,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 28,1</t>
+          <t>14,01; 28,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 23,27</t>
+          <t>11,28; 22,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,12; 26,17</t>
+          <t>10,8; 24,9</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,13; 37,89</t>
+          <t>27,34; 38,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 26,99</t>
+          <t>17,85; 27,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,17; 27,49</t>
+          <t>15,99; 26,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 16,09</t>
+          <t>1,61; 16,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 15,26</t>
+          <t>4,68; 16,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 17,69</t>
+          <t>4,78; 17,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 32,22</t>
+          <t>22,84; 32,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 22,83</t>
+          <t>15,28; 22,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 22,63</t>
+          <t>14,01; 22,55</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,64; 55,88</t>
+          <t>30,99; 56,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 33,78</t>
+          <t>17,91; 34,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,01; 27,51</t>
+          <t>11,68; 26,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 28,21</t>
+          <t>5,46; 25,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 15,49</t>
+          <t>2,85; 16,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,47; 42,58</t>
+          <t>23,9; 42,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,84; 25,72</t>
+          <t>13,74; 25,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 18,61</t>
+          <t>8,61; 18,14</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,24</t>
+          <t>0,0; 67,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 26,57</t>
+          <t>6,42; 29,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 32,92</t>
+          <t>10,45; 31,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 23,04</t>
+          <t>2,84; 23,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,94; 24,91</t>
+          <t>5,82; 25,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,97; 30,93</t>
+          <t>11,3; 31,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 18,47</t>
+          <t>2,46; 20,05</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,75; 30,73</t>
+          <t>24,02; 30,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,57</t>
+          <t>16,95; 22,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,13; 22,83</t>
+          <t>16,24; 23,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,31</t>
+          <t>5,14; 12,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,12</t>
+          <t>6,51; 12,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,52</t>
+          <t>6,27; 12,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,97; 24,58</t>
+          <t>19,17; 24,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,86; 18,39</t>
+          <t>14,21; 18,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,08</t>
+          <t>13,28; 18,27</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10117; 25641</t>
+          <t>10375; 26404</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11512; 28707</t>
+          <t>12311; 28569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10256; 26832</t>
+          <t>9687; 27035</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6259</t>
+          <t>0; 6145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4746</t>
+          <t>0; 5665</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3085; 14029</t>
+          <t>2965; 12855</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12294; 28934</t>
+          <t>10604; 28112</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13086; 30867</t>
+          <t>12829; 30283</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15655; 35531</t>
+          <t>16127; 35488</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6463; 19354</t>
+          <t>6473; 18830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4099; 15461</t>
+          <t>3905; 15849</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6218; 18835</t>
+          <t>5690; 17488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6322</t>
+          <t>0; 6091</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 10840</t>
+          <t>0; 9586</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5176; 17122</t>
+          <t>4458; 16755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8370; 21460</t>
+          <t>7736; 22332</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5878; 18234</t>
+          <t>5346; 19548</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14042; 30748</t>
+          <t>13466; 30238</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17885; 34815</t>
+          <t>17529; 35076</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19817; 41559</t>
+          <t>19998; 42211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11876; 28369</t>
+          <t>12652; 28026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5708</t>
+          <t>0; 5431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>944; 7806</t>
+          <t>948; 8348</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1779</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17920; 36830</t>
+          <t>18365; 36734</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21962; 45871</t>
+          <t>22245; 45206</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12401; 29173</t>
+          <t>12040; 27762</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73817; 103094</t>
+          <t>74408; 104672</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56042; 86071</t>
+          <t>56935; 87425</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36836; 62616</t>
+          <t>36416; 61180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1019; 10195</t>
+          <t>1020; 10236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5126; 17269</t>
+          <t>5296; 18331</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3920; 15336</t>
+          <t>4147; 15529</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76649; 108084</t>
+          <t>76622; 109221</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64887; 98640</t>
+          <t>66019; 98942</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43390; 71165</t>
+          <t>44046; 70915</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20120; 35531</t>
+          <t>19709; 35902</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22641; 42944</t>
+          <t>22771; 43230</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14016; 29630</t>
+          <t>12582; 28905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1880; 10012</t>
+          <t>1939; 9195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1972; 10755</t>
+          <t>1978; 11432</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7290</t>
+          <t>0; 6662</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24249; 42189</t>
+          <t>23677; 41768</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27205; 50564</t>
+          <t>27009; 49524</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15208; 33104</t>
+          <t>15317; 32261</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1460</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4045</t>
+          <t>0; 4069</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1703</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3657; 13016</t>
+          <t>3145; 14429</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6584; 20062</t>
+          <t>6366; 19374</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>999; 8325</t>
+          <t>1026; 8445</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3239; 13577</t>
+          <t>3170; 13976</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7344; 20711</t>
+          <t>7563; 21340</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1013; 7702</t>
+          <t>1027; 8361</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>148095; 191653</t>
+          <t>149806; 192369</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>137926; 184183</t>
+          <t>138297; 185369</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97643; 138260</t>
+          <t>98347; 139481</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13395; 33379</t>
+          <t>12894; 30914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23354; 46612</t>
+          <t>25023; 48116</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21187; 41886</t>
+          <t>20967; 41885</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>165899; 214939</t>
+          <t>167635; 214024</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>166381; 220801</t>
+          <t>170580; 226125</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>125776; 169980</t>
+          <t>124794; 171739</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$medico-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,82; 27,54</t>
+          <t>10,67; 26,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 25,49</t>
+          <t>10,85; 25,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 28,96</t>
+          <t>10,67; 28,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,14</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 20,94</t>
+          <t>4,85; 21,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 20,99</t>
+          <t>8,55; 20,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 18,49</t>
+          <t>7,56; 18,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 22,93</t>
+          <t>10,28; 22,64</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 23,58</t>
+          <t>8,05; 23,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 17,62</t>
+          <t>3,8; 16,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 24,0</t>
+          <t>8,4; 25,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,05</t>
+          <t>0,0; 15,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,73</t>
+          <t>0,0; 17,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 25,03</t>
+          <t>6,71; 24,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 18,56</t>
+          <t>6,56; 17,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,58</t>
+          <t>3,71; 13,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 21,63</t>
+          <t>9,51; 22,82</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 32,87</t>
+          <t>16,16; 32,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,35; 26,06</t>
+          <t>11,99; 25,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 28,52</t>
+          <t>12,11; 28,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,28</t>
+          <t>0,0; 22,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 23,74</t>
+          <t>2,67; 23,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 28,02</t>
+          <t>13,88; 27,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 22,93</t>
+          <t>11,54; 23,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 24,9</t>
+          <t>10,43; 25,12</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,34; 38,47</t>
+          <t>26,74; 37,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 27,41</t>
+          <t>17,68; 27,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 26,86</t>
+          <t>16,28; 26,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 16,16</t>
+          <t>1,63; 16,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,2</t>
+          <t>4,58; 15,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 17,92</t>
+          <t>4,59; 18,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,84; 32,56</t>
+          <t>23,03; 32,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,9</t>
+          <t>14,82; 22,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 22,55</t>
+          <t>13,67; 22,54</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,99; 56,46</t>
+          <t>31,92; 56,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,91; 34,0</t>
+          <t>17,82; 34,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,68; 26,84</t>
+          <t>12,72; 28,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 25,9</t>
+          <t>5,58; 28,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 16,46</t>
+          <t>2,93; 15,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,9; 42,15</t>
+          <t>23,33; 41,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,74; 25,19</t>
+          <t>13,9; 25,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,14</t>
+          <t>8,58; 19,09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,63</t>
+          <t>0,0; 68,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 29,45</t>
+          <t>6,53; 28,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,45; 31,79</t>
+          <t>11,37; 32,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 23,37</t>
+          <t>2,81; 23,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 25,64</t>
+          <t>7,01; 25,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,3; 31,87</t>
+          <t>10,57; 31,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 20,05</t>
+          <t>2,45; 19,88</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,02; 30,85</t>
+          <t>23,8; 30,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,71</t>
+          <t>16,94; 22,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,04</t>
+          <t>16,32; 22,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,33</t>
+          <t>5,37; 12,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 12,52</t>
+          <t>6,52; 12,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,52</t>
+          <t>6,13; 12,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,48</t>
+          <t>19,19; 24,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,21; 18,84</t>
+          <t>14,08; 18,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,28; 18,27</t>
+          <t>13,28; 18,15</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10375; 26404</t>
+          <t>10228; 25713</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12311; 28569</t>
+          <t>12156; 28623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9687; 27035</t>
+          <t>9964; 26930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6145</t>
+          <t>0; 6130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5665</t>
+          <t>0; 5342</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2965; 12855</t>
+          <t>2976; 13023</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10604; 28112</t>
+          <t>11450; 27696</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12829; 30283</t>
+          <t>12379; 30024</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16127; 35488</t>
+          <t>15914; 35029</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6473; 18830</t>
+          <t>6427; 18919</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3905; 15849</t>
+          <t>3418; 14782</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5690; 17488</t>
+          <t>6117; 18472</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6091</t>
+          <t>0; 6298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 9586</t>
+          <t>0; 9376</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4458; 16755</t>
+          <t>4488; 16605</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7736; 22332</t>
+          <t>7887; 21320</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5346; 19548</t>
+          <t>5336; 19691</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13466; 30238</t>
+          <t>13295; 31897</t>
         </is>
       </c>
     </row>
@@ -1965,27 +1965,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17529; 35076</t>
+          <t>17243; 35078</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19998; 42211</t>
+          <t>19425; 41816</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12652; 28026</t>
+          <t>11903; 28048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5431</t>
+          <t>0; 5566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>948; 8348</t>
+          <t>940; 8139</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18365; 36734</t>
+          <t>18196; 35819</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22245; 45206</t>
+          <t>22746; 46426</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12040; 27762</t>
+          <t>11627; 28005</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74408; 104672</t>
+          <t>72754; 103321</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56935; 87425</t>
+          <t>56393; 86680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36416; 61180</t>
+          <t>37070; 61014</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1020; 10236</t>
+          <t>1030; 10172</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5296; 18331</t>
+          <t>5178; 17994</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4147; 15529</t>
+          <t>3979; 16089</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76622; 109221</t>
+          <t>77269; 109494</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>66019; 98942</t>
+          <t>64027; 97747</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44046; 70915</t>
+          <t>42995; 70863</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19709; 35902</t>
+          <t>20295; 36215</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22771; 43230</t>
+          <t>22661; 43598</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12582; 28905</t>
+          <t>13703; 30374</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1939; 9195</t>
+          <t>1980; 10280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1978; 11432</t>
+          <t>2032; 10670</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6662</t>
+          <t>0; 7012</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23677; 41768</t>
+          <t>23112; 41502</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27009; 49524</t>
+          <t>27319; 49706</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15317; 32261</t>
+          <t>15257; 33965</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4069</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3145; 14429</t>
+          <t>3198; 13760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6366; 19374</t>
+          <t>6926; 19717</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1026; 8445</t>
+          <t>1014; 8486</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3170; 13976</t>
+          <t>3819; 13807</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7563; 21340</t>
+          <t>7080; 21253</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1027; 8361</t>
+          <t>1021; 8293</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>149806; 192369</t>
+          <t>148416; 190544</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>138297; 185369</t>
+          <t>138274; 185072</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98347; 139481</t>
+          <t>98799; 136657</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12894; 30914</t>
+          <t>13457; 31506</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25023; 48116</t>
+          <t>25072; 47480</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20967; 41885</t>
+          <t>20517; 41642</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>167635; 214024</t>
+          <t>167818; 217498</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>170580; 226125</t>
+          <t>169033; 221706</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>124794; 171739</t>
+          <t>124842; 170634</t>
         </is>
       </c>
     </row>
